--- a/www/download/COUNTRY.SWE.rpO1.xlsx
+++ b/www/download/COUNTRY.SWE.rpO1.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>Suécia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>7.1209853786912</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>6.70421035800362</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>7.62718343458456</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>7.94723073282277</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>8.26104914409274</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>9.13075211422837</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>10.3114045632859</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>9.70685325223753</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>8.06776946061647</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>7.33729552481548</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>7.44934438059463</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>7.36702534389249</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>6.75082699066162</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.51703522574423</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.60913399607839</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>4.129</t>
+          <t>2.43406959053595</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.096</t>
+          <t>2.34451858096284</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>4.043</t>
+          <t>2.27493198584509</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4.111</t>
+          <t>2.26325010820376</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4.198</t>
+          <t>2.37383719431583</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.301</t>
+          <t>2.42403707309353</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.391</t>
+          <t>2.38237625405235</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.393</t>
+          <t>2.40100892573164</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4.368</t>
+          <t>2.65824507018357</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.337</t>
+          <t>2.46454854051147</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>4.349</t>
+          <t>2.5220434454994</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>4.423</t>
+          <t>2.49079205015269</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>4.524</t>
+          <t>2.45301372748389</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>4.542</t>
+          <t>2.32611227056592</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>4.425</t>
+          <t>2.25216012110131</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.848</t>
+          <t>3.72184914611833</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.819</t>
+          <t>3.56837137367809</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3.768</t>
+          <t>3.44888294569979</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.836</t>
+          <t>3.42082094704266</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>3.918</t>
+          <t>3.57720616641073</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>4.023</t>
+          <t>3.51737456969246</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4.124</t>
+          <t>3.39995145360041</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>4.134</t>
+          <t>3.4813381280074</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>4.128</t>
+          <t>3.61590373929681</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4.091</t>
+          <t>3.47603019489135</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>4.103</t>
+          <t>3.51351723699528</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>3.42827949030335</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>4.268</t>
+          <t>3.35199293141188</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>4.321</t>
+          <t>3.2847369013056</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>4.228</t>
+          <t>3.19849115749007</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6772.82</t>
+          <t>4.12140350013668</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>6770.69</t>
+          <t>4.0119051299689</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>6703.5</t>
+          <t>3.90747600164849</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>6809.79</t>
+          <t>3.90058450557726</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>6988.38</t>
+          <t>4.09383886755038</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7061.95</t>
+          <t>3.99161544240371</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>7105.7</t>
+          <t>3.83005988389724</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>7006.6</t>
+          <t>3.95387669560603</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>6908.1</t>
+          <t>3.64988772165449</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>6963.43</t>
+          <t>3.86786829235368</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>6979.96</t>
+          <t>3.86305543575632</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>3.73074435626734</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>7319.33</t>
+          <t>3.44785065996888</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>7362.323</t>
+          <t>3.39431689474338</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>7146.911</t>
+          <t>3.38169405571726</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6234.64</t>
+          <t>10624423264975.6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>6244.23</t>
+          <t>10562183887490.5</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>6174.71</t>
+          <t>10063759221230.3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>6277.92</t>
+          <t>11289162204696.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>6444.15</t>
+          <t>12121884777132.8</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>6539.08</t>
+          <t>13604778652915.3</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>6609.93</t>
+          <t>13667782660149.5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6527.4</t>
+          <t>14283966206423.6</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>6446.22</t>
+          <t>16703557080736.3</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>6489.13</t>
+          <t>15761279179941.1</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6490.82</t>
+          <t>14500735028668.3</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6587.61</t>
+          <t>13073568089251.5</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>6822.76</t>
+          <t>11485981756918.4</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6920.38</t>
+          <t>8624631636576.87</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6705.67</t>
+          <t>6922657845828.98</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>17.56</t>
+          <t>2388629202792.09</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>17.85</t>
+          <t>2422876347521.64</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>18.25</t>
+          <t>2260809233855.73</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>18.55</t>
+          <t>2514062684262</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>19.98</t>
+          <t>2663279218005.94</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>3005248408271.49</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>22.52</t>
+          <t>3038734062846.46</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>23.11</t>
+          <t>3204467786881.32</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>22.08</t>
+          <t>3769142961089.12</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>3530717064412.34</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>24.91</t>
+          <t>3198152827979.36</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>25.94</t>
+          <t>2872044470485.51</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>26.26</t>
+          <t>2525889571067.58</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>27.98</t>
+          <t>1997382936738.94</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>1639659094032.68</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>56.83</t>
+          <t>884068571.154658</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>57.47</t>
+          <t>825488547.307721</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>58.03</t>
+          <t>846048929.094722</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>58.6</t>
+          <t>948708112.833771</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>57.42</t>
+          <t>1010813943.06032</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>58.29</t>
+          <t>1147073968.04096</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>58.35</t>
+          <t>1226394567.46454</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>58.41</t>
+          <t>1183220083.07825</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>58.34</t>
+          <t>1127110438.72822</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>58.53</t>
+          <t>918915188.750253</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>58.13</t>
+          <t>807946127.76263</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>57.46</t>
+          <t>664887072.171172</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>57.04</t>
+          <t>497018973.548068</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>56.12</t>
+          <t>342051088.714273</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>53.01</t>
+          <t>339758194.657864</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>25.61</t>
+          <t>294803.723292731</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>24.68</t>
+          <t>336644.921951737</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>313917.760906402</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>22.85</t>
+          <t>319244.544569752</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>22.61</t>
+          <t>318515.482118483</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>317600.887566823</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>19.13</t>
+          <t>306013.634153545</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>18.49</t>
+          <t>339666.794669754</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>19.58</t>
+          <t>423979.33754236</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>17.66</t>
+          <t>483439.11952559</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>16.97</t>
+          <t>490439.275952524</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>16.6</t>
+          <t>507886.895964812</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>16.7</t>
+          <t>598667.6121334</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>637875.324693218</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>550558.18538744</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>12.74</t>
+          <t>477638.823639955</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>12.92</t>
+          <t>533345.238454462</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>13.34</t>
+          <t>497501.495941634</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13.71</t>
+          <t>506462.219707482</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>14.64</t>
+          <t>506919.068092304</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>16.49</t>
+          <t>501645.214145521</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>17.27</t>
+          <t>476546.390687192</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>520704.166493948</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>17.98</t>
+          <t>639790.351953341</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>725594.965163918</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>19.89</t>
+          <t>747258.623728116</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>21.03</t>
+          <t>781491.046797919</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>21.56</t>
+          <t>915625.538267309</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>23.03</t>
+          <t>916003.518434327</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>24.09</t>
+          <t>765468.384948103</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>58.57</t>
+          <t>3.48247763902001</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>59.15</t>
+          <t>3.34948286612086</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>59.74</t>
+          <t>3.23727840014695</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.24</t>
+          <t>3.21446822118743</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>59.43</t>
+          <t>3.3471298295114</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>60.73</t>
+          <t>3.26195613203208</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>60.91</t>
+          <t>3.14723922677356</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>3.20613194979985</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>61.48</t>
+          <t>3.32404990467478</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>61.25</t>
+          <t>3.19872071751742</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>60.96</t>
+          <t>3.22717304870096</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>60.36</t>
+          <t>3.14256064947788</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>60.37</t>
+          <t>3.05049920433421</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>59.85</t>
+          <t>2.94975498607655</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>56.63</t>
+          <t>2.8666314822584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>28.69</t>
+          <t>48664.0245698599</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>27.93</t>
+          <t>53484.099109837</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>26.92</t>
+          <t>50572.9831406212</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>26.06</t>
+          <t>52046.5431885725</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>25.93</t>
+          <t>54864.259842949</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>22.78</t>
+          <t>53432.1445377011</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>48358.4082237311</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>21.3</t>
+          <t>52006.600409208</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>20.55</t>
+          <t>62542.9067994847</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>20.04</t>
+          <t>64230.6436042982</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>19.15</t>
+          <t>65520.3671164255</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>18.6</t>
+          <t>67553.0926450966</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>18.07</t>
+          <t>77102.2193546365</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>17.11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>19.28</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>7.1209853786912</t>
+          <t>620777.899785447</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6.70421035800362</t>
+          <t>634410.29235265</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>7.62718343458456</t>
+          <t>600002.450598653</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7.94723073282277</t>
+          <t>655335.266861819</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.26104914409274</t>
+          <t>679824.182663772</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>9.13075211422837</t>
+          <t>747035.324833203</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10.3114045632859</t>
+          <t>736912.906888753</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>9.70685325223753</t>
+          <t>775111.941095972</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>8.06776946061647</t>
+          <t>913156.061897742</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7.33729552481548</t>
+          <t>863002.802212637</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>7.44934438059463</t>
+          <t>779428.940334216</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>7.36702534389249</t>
+          <t>688673.621351792</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>6.75082699066162</t>
+          <t>591834.291119188</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>6.51703522574423</t>
+          <t>462282.254435377</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>7.60913399607839</t>
+          <t>387778.57278441</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>194901469619.687</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>20280565471.8538</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>41159768961.7297</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>50096061925.188</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>145882254960.949</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>338682238599.551</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.129</t>
+          <t>227669983711.115</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.141</t>
+          <t>241405593213.045</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.175</t>
+          <t>353715799506.406</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.198</t>
+          <t>449597055840.937</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.202</t>
+          <t>529272966262.786</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>672740640116.51</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>544892269563.704</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>493745484999.056</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>304665510238.231</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.143</t>
+          <t>282490893618.894</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>114501543108.398</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>142819020019.19</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>205180336552.704</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>317847271060.945</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.145</t>
+          <t>360665793451.329</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.137</t>
+          <t>247372497980.752</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>232861139242.914</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>279126344878.517</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.211</t>
+          <t>301401165616.721</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>328704114153.934</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.225</t>
+          <t>421903399746.67</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>297245629963.305</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>292614986861.827</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.237</t>
+          <t>135218770797.709</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.545</t>
+          <t>-87589423999.2066</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>-94220977636.5442</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>-101659251057.46</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>-155084274627.516</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>-171965016099.997</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>-21983554851.7774</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.517</t>
+          <t>-19702514269.6371</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>8544453970.13147</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>74589454627.8888</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>148195890224.216</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.809</t>
+          <t>200568852108.852</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.855</t>
+          <t>250837240369.84</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.986</t>
+          <t>247646639600.398</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>201130498137.229</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>169446739440.521</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.462</t>
+          <t>2782623.05458607</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.502</t>
+          <t>2759356.69667857</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>2542377.42395691</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>2761889.65641252</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.476</t>
+          <t>2955283.98328089</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>3183831.78351745</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>3056154.11416477</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.466</t>
+          <t>3260223.10011515</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.574</t>
+          <t>3948532.38240213</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>3623507.74492579</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.694</t>
+          <t>3294781.00995835</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>2852872.24414536</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>2397224.32527597</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>1825901.63943084</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.757</t>
+          <t>1499396.83767343</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>2824631.73402818</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>2911364.53396477</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>2823236.27358737</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>3137550.35228429</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>3322653.10562818</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>3724882.0403815</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>3694431.44847207</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>3895250.63521913</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>4635555.5229917</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>4458989.81817163</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>4072367.67452557</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>3617782.97018981</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>3127129.70400615</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>2473300.72440787</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>2103875.59812541</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>243.41</t>
+          <t>96725.5237641605</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>234.45</t>
+          <t>102366.696057867</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>227.49</t>
+          <t>101699.771226788</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>226.33</t>
+          <t>104969.377987809</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>237.38</t>
+          <t>107075.320954573</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>242.4</t>
+          <t>110832.788765628</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>238.24</t>
+          <t>100696.185240731</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>240.1</t>
+          <t>106311.677138873</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>265.82</t>
+          <t>130882.297248063</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>246.45</t>
+          <t>159190.879264687</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>252.2</t>
+          <t>170943.424743657</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>249.08</t>
+          <t>192960.40986097</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>245.3</t>
+          <t>226789.430813134</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>232.61</t>
+          <t>248132.595279107</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>225.22</t>
+          <t>181913.166040362</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>372.18</t>
+          <t>2885922272941.72</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>356.84</t>
+          <t>2851683166148.86</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>344.89</t>
+          <t>2854641423008.82</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>342.08</t>
+          <t>3248790842544.69</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>357.72</t>
+          <t>3422826102932.98</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>351.74</t>
+          <t>3874171824910.6</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>3796134684856.43</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>348.13</t>
+          <t>3892959433081.55</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>361.59</t>
+          <t>4526229510609.42</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>347.6</t>
+          <t>4436463455408.76</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>351.35</t>
+          <t>4110135664924.14</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>342.83</t>
+          <t>3789453267282.93</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>335.2</t>
+          <t>3290444290705.74</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>328.47</t>
+          <t>2520394731062.29</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>319.85</t>
+          <t>1884141087957.35</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>412.14</t>
+          <t>75831.3495973377</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>401.19</t>
+          <t>79890.6155496373</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>390.75</t>
+          <t>78082.0581520606</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>390.06</t>
+          <t>83083.1034853668</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>409.38</t>
+          <t>85453.4305373733</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>399.16</t>
+          <t>89747.980114205</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>383.01</t>
+          <t>81785.0223451439</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>395.39</t>
+          <t>85720.0656918854</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>364.99</t>
+          <t>104826.942952039</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>386.79</t>
+          <t>123953.538242074</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>386.31</t>
+          <t>136436.242345256</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>373.07</t>
+          <t>155369.566848147</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>344.79</t>
+          <t>186026.553897001</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>339.43</t>
+          <t>208723.923020259</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>338.17</t>
+          <t>152138.611332661</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>11662621.967</t>
+          <t>2318250237799.53</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11924366.858</t>
+          <t>2140484310419.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11414908.901</t>
+          <t>2108489642711.31</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>12899724.518</t>
+          <t>2478123041816.4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>13947500.942</t>
+          <t>2695677045334.52</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>16019600.191</t>
+          <t>3253422711159.07</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>16222987.377</t>
+          <t>3098433839402.84</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>17113004.616</t>
+          <t>3162950969228.66</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>20247642.969</t>
+          <t>3722134708292.67</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>19340422.437</t>
+          <t>3601676796444.13</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>17710319.78</t>
+          <t>3521244418744.57</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>15999645.186</t>
+          <t>3423708865291.51</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>14148072.92</t>
+          <t>3006195348466.47</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>11232856.993</t>
+          <t>2421647416095.67</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>9309357.675</t>
+          <t>1748327245326.89</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>10706976.989</t>
+          <t>20894.1741668229</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>10538259.16</t>
+          <t>22476.0805082296</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>9579678.133</t>
+          <t>23617.7130747272</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>10595437.289</t>
+          <t>21886.274502442</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>11577620.533</t>
+          <t>21621.8904171997</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>12808236.882</t>
+          <t>21084.8086514232</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>12602357.105</t>
+          <t>18911.1628955872</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>13478414.341</t>
+          <t>20591.611446988</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>16297962.262</t>
+          <t>26055.3542960244</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>14824494.886</t>
+          <t>35237.341022613</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>13519145.44</t>
+          <t>34507.182398401</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>11897618.407</t>
+          <t>37590.8430128234</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>10231113.698</t>
+          <t>40762.8769161332</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>7889173.213</t>
+          <t>39408.6722588476</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>6339957.473</t>
+          <t>29774.5547077013</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>10624423.265</t>
+          <t>567672035142.192</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>10562183.887</t>
+          <t>711198855729.156</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>10063759.221</t>
+          <t>746151780297.502</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>11289162.205</t>
+          <t>770667800728.297</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>12121884.777</t>
+          <t>727149057598.461</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>13604778.653</t>
+          <t>620749113751.538</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>13667782.66</t>
+          <t>697700845453.586</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>14283966.206</t>
+          <t>730008463852.888</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>16703557.081</t>
+          <t>804094802316.756</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>15761279.18</t>
+          <t>834786658964.628</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>14500735.029</t>
+          <t>588891246179.571</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>13073568.089</t>
+          <t>365744401991.42</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>11485981.757</t>
+          <t>284248942239.264</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>8624631.637</t>
+          <t>98747314966.6195</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>6922657.846</t>
+          <t>135813842630.458</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.478</t>
+          <t>114854.61053</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>122774.93584</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.498</t>
+          <t>112054.99439</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>112549.77093</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.507</t>
+          <t>113330.15737</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.502</t>
+          <t>108058.67783</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.477</t>
+          <t>99019.68258</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.521</t>
+          <t>110070.99521</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>138070.00793</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.726</t>
+          <t>158839.5881</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.747</t>
+          <t>160076.10059</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.781</t>
+          <t>172003.34448</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.916</t>
+          <t>199903.80459</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.916</t>
+          <t>208735.56022</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.765</t>
+          <t>167415.59572</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6557506.177</t>
+          <t>0.0535880004430437</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>6666799.128</t>
+          <t>0.0446475249065349</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6350117.109</t>
+          <t>0.0447102742219196</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>7116036.116</t>
+          <t>0.0425321401521922</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7616616.176</t>
+          <t>0.044700616629324</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8613437.652</t>
+          <t>0.0349235375180972</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>8776748.548</t>
+          <t>0.0276544014955168</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>9317745.716</t>
+          <t>0.0323535428974781</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>11069193.282</t>
+          <t>0.0403038827323497</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>10501201.49</t>
+          <t>0.0547857361478185</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>9517093.229</t>
+          <t>0.054832707452759</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>8496442.721</t>
+          <t>0.0666301044100791</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>7509931.718</t>
+          <t>0.0647866830108882</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>6005915.474</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>4979076.885</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>133127.784362746</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>150511.0878089</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>136807.643597456</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>137032.009325101</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.319</t>
+          <t>136351.930258648</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>135897.23871761</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>128638.440508168</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>140953.50530439</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>174679.259001201</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.483</t>
+          <t>198006.744264434</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>201662.713361205</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.508</t>
+          <t>211588.521117675</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.599</t>
+          <t>248571.027188134</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>262905.781776772</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.551</t>
+          <t>222136.709758279</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2388629.203</t>
+          <t>143141.090244378</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2422876.348</t>
+          <t>161542.668371692</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2260809.234</t>
+          <t>147085.249329839</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2514062.684</t>
+          <t>147365.163379276</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2663279.218</t>
+          <t>146513.806072053</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>3005248.408</t>
+          <t>145381.994219881</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>3038734.063</t>
+          <t>136976.405454252</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>3204467.787</t>
+          <t>149877.465676238</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>3769142.961</t>
+          <t>185578.561508121</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>3530717.064</t>
+          <t>210743.792381888</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3198152.828</t>
+          <t>215298.41297581</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>2872044.47</t>
+          <t>225476.100933943</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>2525889.571</t>
+          <t>264880.656011057</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>1997382.937</t>
+          <t>280324.241073704</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>1639659.094</t>
+          <t>237231.086161039</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>348.25</t>
+          <t>545298.549566519</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>334.95</t>
+          <t>595671.882688816</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>323.73</t>
+          <t>546296.317448332</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321.45</t>
+          <t>550559.584078313</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>334.71</t>
+          <t>559827.924355327</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>326.2</t>
+          <t>546059.288310521</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>314.72</t>
+          <t>516590.591712231</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>320.61</t>
+          <t>572674.271663728</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>332.4</t>
+          <t>700425.904121031</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>319.87</t>
+          <t>789646.203294406</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>322.72</t>
+          <t>808590.697184944</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>314.26</t>
+          <t>855373.532513009</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>305.05</t>
+          <t>985730.606451543</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>294.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>286.66</t>
+          <t>0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>884.069</t>
+          <t>143141.090244378</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>825.489</t>
+          <t>149845.764626259</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>846.049</t>
+          <t>153009.12433474</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>948.708</t>
+          <t>158833.376482047</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>1010.814</t>
+          <t>162872.121386245</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>1147.074</t>
+          <t>178176.232055176</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1226.395</t>
+          <t>190976.721517479</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1183.22</t>
+          <t>196148.574637276</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1127.11</t>
+          <t>198444.141333506</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>918.915</t>
+          <t>204866.178068768</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>807.946</t>
+          <t>215662.279492884</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>664.887</t>
+          <t>220237.056421005</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>497.019</t>
+          <t>233223.897723086</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>342.051</t>
+          <t>236013.372408089</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>339.758</t>
+          <t>228839.713418951</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>133127.784362746</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>139368.926890817</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>142042.186841521</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>147728.752951229</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>151644.686131021</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>166730.278943514</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>179849.433456003</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>185100.922674331</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>187522.568122355</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>193222.90210259</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>201851.287700017</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>207426.50935102</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>220500.176045215</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>223347.6713283</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>215879.258804695</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>77885.4834856216</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>80079.3743283085</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>74998.0413001609</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>75463.020580724</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>79888.9132679466</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>72502.466580119</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>62644.4118557478</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>70534.6420237624</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>90772.7903018787</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>107491.992148112</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>109857.58426419</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>124546.720426057</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>140964.435688943</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>150830.402136296</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>116473.816238961</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>10706976989425.7</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>10538259160274.8</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>9579678133469.64</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>10595437288895.4</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>11577620532911.4</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>12808236881912.3</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>12602357105169.8</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>13478414340505.9</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>16297962261603</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>14824494886040.4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>13519145440061.1</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>11897618406983.8</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>10231113697845.3</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>7889173213488.82</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>6339957473158.06</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>11662621966617.2</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>11924366858201</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>11414908901368.5</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>12899724518381.6</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>13947500941515.8</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>16019600191088.5</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>16222987376530.5</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>17113004615728.5</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>20247642968875.4</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>19340422437337.6</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>17710319779744.2</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>15999645185664.4</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>14148072919835</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>11232856993161.9</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>9309357674889.96</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>6557506176913.54</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>6666799127611.85</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>6350117108794.42</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>7116036115574.08</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>7616616176036.46</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>8613437651699.86</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>8776748548282.69</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>9317745715720.86</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>11069193281939.4</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>10501201490044</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>9517093229059.91</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>8496442720925.4</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>7509931717757.17</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>6005915473931.99</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4979076884953.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>4128899.99999584</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4095799.9999959</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>4043200</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>4111400</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>4197700.00000615</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4300700.00000532</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4391200</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4393300.00000522</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4367900</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4337400</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4348900</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4422500</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4524300</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4541646.26335567</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4424861.28133468</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>3847799.99999621</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>3819099.99999627</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>3768000</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>3836300</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3917600.00000346</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>4022900</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>4123600</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>4134200.00000303</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>4127600</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>4091200</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>4103200</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>4170400</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>4267900</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>4320700</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>4228338.56512301</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>6772819999.99282</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>6770689999.99285</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>6703500000</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6809790000</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>6988380000.0107</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>7061950000.00911</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>7105700000</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>7006600000.00862</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>6908100000</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>6963430000</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>6979960000</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>7.072e+09</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>7319330000</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>7362323182.22011</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>7146911162.50548</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>6234639999.99358</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>6244229999.9936</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>6174710000</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>6277920000</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>6444150000.00593</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>6539080000</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>6609930000</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>6527400000.00494</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>6446220000</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>6489130000</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>6490820000</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>6587610000</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>6822760000</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>6920380000</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>6705669998.77628</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.175632394391622</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.178519764421943</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.182521612994752</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.185480918571493</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.199769360570896</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.218077092896323</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.225195429041695</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.231065372362702</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.22077703781729</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.238035604533249</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.249053314488781</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.25943802992654</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.262575913097484</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.27981093651643</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.292918479894697</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.568263560293997</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.574674634470877</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.580260119671008</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.586000513061219</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.574163857675759</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.582930939050782</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.583532617697635</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.584072145887833</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.583415741425941</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.585317212081492</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.581267224553589</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.574570886085595</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.570379798923343</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.561167767493832</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.530134638009854</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.256104045314381</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.24680560110718</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.23721826733424</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.228518568367287</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.226066781753345</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.198991968052896</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.19127195326067</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.184862481749466</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.195807220756769</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.176647183385259</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.16967946095763</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.165991083987865</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.167044287979174</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.159021295989738</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.176946882095448</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.127366819728121</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.129160847897513</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.133416182165984</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.137055627698075</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.1464484811306</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.164891415642487</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.172730142899479</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.176779161263421</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.179782694531231</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.187163260028709</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.198873353722608</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.210336155623757</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.215609489132964</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.230321399524585</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.240881984702742</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.585702966243725</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.591529283873456</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.597372678209279</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.602366870709266</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.594291764382177</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.607277147009464</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.609096810665625</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.610223712014477</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.614762393708153</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.612470415297403</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.609644581664782</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.603618796500982</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.603726782905289</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.598529920241151</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.566309634240847</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.286930214028155</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.279309868229031</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.269211139624737</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.26057750159266</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.259259754487222</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.227831437348049</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.218173046434896</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.212997126722102</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.205454911760616</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.200366324673888</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.19148206461261</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.186045047875261</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.180663727961747</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.171148680234264</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.192808381056411</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>461976.65331</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>501511.41338</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>466168.81334</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>468861.31007</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>476120.03486</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>466126.22559</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>430428.36138</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>466075.03516</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>573860.72027</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>666076.61884</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>694302.57719</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>753739.90604</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>880097.95041</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>949568.28984</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>757060.99647</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>221026.57373</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>241622.0427</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>222083.29063</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>222828.18396</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>226402.71934</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>217884.4608</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>199620.81731</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>220412.1077</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>276351.35181</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>318235.78453</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>325155.99724</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>350022.82136</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>405845.0917</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>431154.64321</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>353704.9024</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3883063.05764445</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>4018765.57132922</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>4144897.71115209</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>4291173.96676717</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>4451909.0550342</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>4621620.99180891</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>4765026.77031318</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>4883940.32262649</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>5000945.27065932</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>5138989.3150617</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>5306922.67425119</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>5502674.76391365</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>5725293.18762794</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 1</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO1</t>
